--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>652.04</v>
+        <v>649.71</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1287608.75</v>
+        <v>1283024.5</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17881.28</v>
+        <v>17817.62</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>69796.85000000001</v>
+        <v>69548.35000000001</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2271.5</v>
+        <v>2263.41</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2950.37</v>
+        <v>2939.86</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>46423.98</v>
+        <v>46258.69</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18569.59</v>
+        <v>18503.48</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>74278.36</v>
+        <v>74013.91</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>37139.18</v>
+        <v>37006.96</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>972.85</v>
+        <v>969.39</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>389.58</v>
+        <v>388.2</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1209.74</v>
+        <v>1205.44</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>68409.61</v>
+        <v>68166.05</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>16828.03</v>
+        <v>16768.12</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3112.44</v>
+        <v>3101.36</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14279.23</v>
+        <v>14228.39</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10073.13</v>
+        <v>10037.27</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34246.91</v>
+        <v>34124.98</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1291.43</v>
+        <v>1286.84</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>34721.1</v>
+        <v>34597.49</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>68550.42</v>
+        <v>68306.36</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>68409.61</v>
+        <v>68166.05</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>68409.61</v>
+        <v>68166.05</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>736.59</v>
+        <v>733.96</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>300.55</v>
+        <v>298.31</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9509.92</v>
+        <v>9438.75</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9276.610000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9219.52</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9219.52</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>859.84</v>
+        <v>853.41</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>450.41</v>
+        <v>447.04</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2431.03</v>
+        <v>2412.84</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9364.65</v>
+        <v>9294.57</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>9290.02</v>
+        <v>9220.49</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9311.32</v>
+        <v>9241.629999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9739.049999999999</v>
+        <v>9666.16</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>891.73</v>
+        <v>885.0599999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>889.24</v>
+        <v>882.58</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9219.52</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3394.36</v>
+        <v>3368.96</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3819.27</v>
+        <v>3790.69</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>568.75</v>
+        <v>564.49</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>177.21</v>
+        <v>175.88</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>664.88</v>
+        <v>659.9</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>20576.31</v>
+        <v>20422.32</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>389.58</v>
+        <v>386.67</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>25150.11</v>
+        <v>24961.88</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>433.52</v>
+        <v>430.27</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2076.2</v>
+        <v>2060.66</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9219.52</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>18569.59</v>
+        <v>18430.62</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1056.89</v>
+        <v>1048.98</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>52555.46</v>
+        <v>52162.13</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3186.03</v>
+        <v>3162.18</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3124.85</v>
+        <v>3101.47</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1341.85</v>
+        <v>1331.81</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>9732.370000000001</v>
+        <v>9760.57</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>487.69</v>
+        <v>489.1</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9373.639999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>125142.02</v>
+        <v>125504.55</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1937.51</v>
+        <v>1943.13</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>126515.54</v>
+        <v>126882.05</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1245.26</v>
+        <v>1248.87</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1795.93</v>
+        <v>1801.14</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>130469.01</v>
+        <v>130846.97</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9373.639999999999</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>37386.25</v>
+        <v>37494.56</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9373.639999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>9777.77</v>
+        <v>9806.09</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1973.12</v>
+        <v>1978.83</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11972.41</v>
+        <v>12034.25</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>23288.57</v>
+        <v>23408.87</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>18505.68</v>
+        <v>18601.27</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>129.11</v>
+        <v>129.77</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4639.36</v>
+        <v>4663.32</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11574.48</v>
+        <v>11634.27</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>85220.28</v>
+        <v>85660.5</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>120770.21</v>
+        <v>121394.07</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>361.64</v>
+        <v>363.51</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>218981.08</v>
+        <v>220112.26</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>730.1799999999999</v>
+        <v>733.95</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>9634.67</v>
+        <v>9684.440000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>25394.74</v>
+        <v>25525.92</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8477.17</v>
+        <v>8520.959999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>36991.3</v>
+        <v>37182.38</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>6727.59</v>
+        <v>6762.35</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8759.24</v>
+        <v>8804.49</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>350.18</v>
+        <v>348.71</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>850.0700000000001</v>
+        <v>846.48</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>6008.12</v>
+        <v>5982.79</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>10073.13</v>
+        <v>10030.66</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2885.4</v>
+        <v>2873.23</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>609.46</v>
+        <v>606.89</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>831.5599999999999</v>
+        <v>828.05</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>22446.68</v>
+        <v>22352.04</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>9289.02</v>
+        <v>9249.860000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4354.71</v>
+        <v>4336.35</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10058.16</v>
+        <v>10015.75</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>107.93</v>
+        <v>107.47</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>17725</v>
+        <v>17650.26</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>338.81</v>
+        <v>337.38</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1429.72</v>
+        <v>1423.69</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5242.32</v>
+        <v>5220.21</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>542.46</v>
+        <v>540.1799999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2311.96</v>
+        <v>2302.21</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>726.41</v>
+        <v>723.34</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>510.78</v>
+        <v>508.62</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>10159.77</v>
+        <v>10116.93</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>9289.02</v>
+        <v>9249.860000000001</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>10159.77</v>
+        <v>10116.93</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>17642.51</v>
+        <v>17568.13</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>94097.00999999999</v>
+        <v>93700.25999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>46415.88</v>
+        <v>46220.18</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6165.22</v>
+        <v>6139.22</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>46426.75</v>
+        <v>46230.99</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9648.530000000001</v>
+        <v>9607.85</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>476.9</v>
+        <v>474.89</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1430.69</v>
+        <v>1424.66</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1430.69</v>
+        <v>1424.66</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6228.9</v>
+        <v>6202.64</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>63953.42</v>
+        <v>63683.77</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2395.73</v>
+        <v>2385.63</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>752.49</v>
+        <v>749.3200000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3354.02</v>
+        <v>3339.88</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>958.29</v>
+        <v>954.25</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>266.25</v>
+        <v>265.13</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1048.39</v>
+        <v>1043.97</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>958.29</v>
+        <v>954.25</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>19266.3</v>
+        <v>19319.19</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6165.22</v>
+        <v>6182.14</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8120.78</v>
+        <v>8143.08</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>12551.5</v>
+        <v>12585.95</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>636.62</v>
+        <v>638.36</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8759.24</v>
+        <v>8783.290000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>74320.13</v>
+        <v>74524.16</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>18729.3</v>
+        <v>18780.72</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1473.9</v>
+        <v>1477.95</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1569.13</v>
+        <v>1573.44</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1191.75</v>
+        <v>1195.02</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>540.54</v>
+        <v>542.03</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1568.94</v>
+        <v>1573.24</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>365.09</v>
+        <v>366.09</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>14380.48</v>
+        <v>14419.96</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2201.5</v>
+        <v>2207.55</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2766</v>
+        <v>2773.59</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1359.84</v>
+        <v>1363.57</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2888.1</v>
+        <v>2896.03</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>799.17</v>
+        <v>801.37</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1731.12</v>
+        <v>1735.87</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>699.9400000000001</v>
+        <v>706.3099999999999</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>9364.65</v>
+        <v>9449.83</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>18729.3</v>
+        <v>18899.66</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>10411.98</v>
+        <v>10506.69</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1547.27</v>
+        <v>1561.34</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>920.39</v>
+        <v>928.76</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>20658.31</v>
+        <v>20846.21</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>236.45</v>
+        <v>238.6</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>869.39</v>
+        <v>877.29</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1946.74</v>
+        <v>1964.44</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>28990.05</v>
+        <v>29253.73</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8759.24</v>
+        <v>8838.91</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9431.58</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>661.95</v>
+        <v>667.97</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>18693.13</v>
+        <v>18863.15</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>112.94</v>
+        <v>113.96</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5659.15</v>
+        <v>5710.62</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10749.77</v>
+        <v>10847.54</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>7736.65</v>
+        <v>7807.02</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1942.76</v>
+        <v>1960.43</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>4912.78</v>
+        <v>4957.47</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1394.62</v>
+        <v>1407.3</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>757.91</v>
+        <v>764.8099999999999</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>953.15</v>
+        <v>961.8200000000001</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3812.59</v>
+        <v>3847.27</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1906.3</v>
+        <v>1923.64</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>953.15</v>
+        <v>961.8200000000001</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>476.57</v>
+        <v>480.91</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7148.61</v>
+        <v>7213.64</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>522.98</v>
+        <v>526.62</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>57860.82</v>
+        <v>58263.65</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>9569.73</v>
+        <v>9636.360000000001</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>129.11</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>26503.74</v>
+        <v>26688.26</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3841.5</v>
+        <v>3868.25</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>705.03</v>
+        <v>709.9400000000001</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>10073.13</v>
+        <v>10143.26</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>946.53</v>
+        <v>953.12</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>9509.92</v>
+        <v>9576.129999999999</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>389.58</v>
+        <v>392.29</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>6889.71</v>
+        <v>6937.67</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2611.51</v>
+        <v>2629.69</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>11481.8</v>
+        <v>11561.74</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>9290.02</v>
+        <v>9354.690000000001</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>487.69</v>
+        <v>490.9</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1164.86</v>
+        <v>1172.53</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>9509.92</v>
+        <v>9572.549999999999</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>568.75</v>
+        <v>572.49</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>9777.77</v>
+        <v>9842.16</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1202.38</v>
+        <v>1210.3</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>476.57</v>
+        <v>479.71</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>279.38</v>
+        <v>281.22</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>630.99</v>
+        <v>635.14</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1373.58</v>
+        <v>1382.62</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>34767.94</v>
+        <v>34996.92</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1028.46</v>
+        <v>1037.62</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>8759.24</v>
+        <v>8837.26</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9367.49</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9367.49</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1321.03</v>
+        <v>1332.8</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>157666.38</v>
+        <v>159070.67</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2606.86</v>
+        <v>2630.08</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>10916.82</v>
+        <v>11014.06</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3026.83</v>
+        <v>3053.79</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1111.76</v>
+        <v>1121.66</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>9289.02</v>
+        <v>9371.76</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>5114.62</v>
+        <v>5160.17</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>131388.65</v>
+        <v>132558.89</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9367.49</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>8759.24</v>
+        <v>8837.26</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>27854.39</v>
+        <v>28102.48</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>26277.73</v>
+        <v>26511.78</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>5788.07</v>
+        <v>5778.15</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>9509.92</v>
+        <v>9493.620000000001</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>542.9</v>
+        <v>541.96</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2391.58</v>
+        <v>2387.48</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>20370.52</v>
+        <v>20335.61</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>9820.84</v>
+        <v>9804.01</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1400.43</v>
+        <v>1398.03</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>687.9</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>9509.92</v>
+        <v>9493.620000000001</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>751.4299999999999</v>
+        <v>750.15</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>7018.35</v>
+        <v>7006.32</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>26349.88</v>
+        <v>26304.72</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>12143.29</v>
+        <v>12122.48</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>9289.02</v>
+        <v>9273.1</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>745.9</v>
+        <v>745.13</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1363.28</v>
+        <v>1361.87</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9275.219999999999</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>278.74</v>
+        <v>278.45</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9336.92</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>980.75</v>
+        <v>979.73</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>9364.65</v>
+        <v>9354.99</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9275.219999999999</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>13920.4</v>
+        <v>13906.04</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>953.15</v>
+        <v>952.17</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>177.21</v>
+        <v>177.02</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>487.69</v>
+        <v>487.19</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>9569.620000000001</v>
+        <v>9559.75</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>7737.37</v>
+        <v>7729.39</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>9162.68</v>
+        <v>9153.23</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>31987.1</v>
+        <v>31954.11</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1714.73</v>
+        <v>1712.96</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3198.05</v>
+        <v>3175.14</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>520.8</v>
+        <v>517.0700000000001</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>9820.84</v>
+        <v>9750.48</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1876.07</v>
+        <v>1862.63</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2803.65</v>
+        <v>2783.56</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>8866.959999999999</v>
+        <v>8803.440000000001</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9222.49</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>11624.94</v>
+        <v>11541.66</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>540.55</v>
+        <v>536.67</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>522.98</v>
+        <v>519.23</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>398.68</v>
+        <v>395.82</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9218.280000000001</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>868.3200000000001</v>
+        <v>862.1</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>9346.559999999999</v>
+        <v>9279.610000000001</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>768.59</v>
+        <v>763.08</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>770.65</v>
+        <v>765.13</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>13219.46</v>
+        <v>13124.76</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>19661.46</v>
+        <v>19520.61</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9222.49</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>9510.200000000001</v>
+        <v>9496.209999999999</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>568.47</v>
+        <v>567.64</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>18578.07</v>
+        <v>18550.74</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1886.24</v>
+        <v>1883.47</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1029.24</v>
+        <v>1027.72</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>616.8</v>
+        <v>615.89</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2382.87</v>
+        <v>2379.37</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9569.75</v>
+        <v>9555.67</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>9290.02</v>
+        <v>9276.35</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1304.74</v>
+        <v>1302.82</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1219.52</v>
+        <v>1217.73</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>985.54</v>
+        <v>984.09</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>9510.200000000001</v>
+        <v>9496.209999999999</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1229.78</v>
+        <v>1227.97</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3554.35</v>
+        <v>3549.12</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9275.370000000001</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>379.58</v>
+        <v>377.51</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1048.39</v>
+        <v>1042.68</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>266.25</v>
+        <v>264.8</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>9510.200000000001</v>
+        <v>9458.41</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>9364.65</v>
+        <v>9313.65</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>704.38</v>
+        <v>700.55</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3024.08</v>
+        <v>3007.61</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>4029.63</v>
+        <v>4007.69</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>816.13</v>
+        <v>811.6799999999999</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9230.08</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>18569.59</v>
+        <v>18460.16</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9230.08</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>693.6799999999999</v>
+        <v>689.59</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>42019.28</v>
+        <v>41771.66</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>70073.95</v>
+        <v>69661</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>46423.98</v>
+        <v>46150.4</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>524.1900000000001</v>
+        <v>521.1</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>18881.8</v>
+        <v>18770.53</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>153.31</v>
+        <v>152.41</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>476.57</v>
+        <v>473.77</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>953.15</v>
+        <v>947.53</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1048.39</v>
+        <v>1042.21</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>9284.799999999999</v>
+        <v>9228.379999999999</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>87592.42999999999</v>
+        <v>87060.19</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>26277.73</v>
+        <v>26118.06</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1284.4</v>
+        <v>1276.59</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2087.28</v>
+        <v>2074.6</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2016.92</v>
+        <v>2004.66</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1173.54</v>
+        <v>1166.41</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>564.6799999999999</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>16145.87</v>
+        <v>16047.76</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>8847.639999999999</v>
+        <v>8793.870000000001</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>19641.68</v>
+        <v>19522.33</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>486.01</v>
+        <v>483.06</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>18569.59</v>
+        <v>18456.75</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>87592.42999999999</v>
+        <v>87060.19</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>11159.79</v>
+        <v>11091.98</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>18580.03</v>
+        <v>18467.13</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>11808.76</v>
+        <v>11763.19</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>18578.07</v>
+        <v>18506.36</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>4434.73</v>
+        <v>4417.62</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>981.11</v>
+        <v>977.3200000000001</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1591.3</v>
+        <v>1599.54</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>8834.58</v>
+        <v>8880.32</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>19423.38</v>
+        <v>19523.94</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>292.64</v>
+        <v>294.16</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>521.41</v>
+        <v>524.11</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>9711.690000000001</v>
+        <v>9761.969999999999</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>521.41</v>
+        <v>524.11</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>9711.690000000001</v>
+        <v>9761.969999999999</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>11278.35</v>
+        <v>11336.74</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3938.07</v>
+        <v>3958.46</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>717.02</v>
+        <v>720.73</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>786.1900000000001</v>
+        <v>790.26</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>9887.040000000001</v>
+        <v>9938.23</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>8966.209999999999</v>
+        <v>9012.629999999999</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>113870.16</v>
+        <v>114459.71</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>64993.57</v>
+        <v>65330.06</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>30837.49</v>
+        <v>30997.14</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>6747.82</v>
+        <v>6782.76</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4620.4</v>
+        <v>4644.33</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>46398.24</v>
+        <v>46638.46</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>11844.85</v>
+        <v>11906.17</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>9289.030000000001</v>
+        <v>9337.129999999999</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>9714.530000000001</v>
+        <v>9723.889999999999</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>15528.17</v>
+        <v>15543.14</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>28007.37</v>
+        <v>28034.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Heraldo Castro Palma</t>
+          <t>HERALDO CASTRO PALMA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17882,7 +17882,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18370,7 +18370,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -20993,7 +20993,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2026.xlsx
@@ -684,7 +684,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1420,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1485,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2465,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2530,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2839,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2904,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3152,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3217,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3526,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3591,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3778,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4026,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4091,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4156,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4465,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5018,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5083,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5148,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5274,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5583,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5709,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6018,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6144,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6209,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6274,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6339,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6526,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6652,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7266,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7331,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7396,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7461,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8018,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8144,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8209,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8274,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8339,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8526,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8713,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9205,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9331,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9518,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9644,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9770,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +9896,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10083,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10148,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10213,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10278,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10343,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10408,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10473,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10538,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10725,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +10912,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11038,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11164,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11717,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +11843,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +11908,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12156,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12282,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12408,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12473,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12599,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12664,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +12790,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +12855,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13164,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13229,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13294,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +13725,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +13851,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +13977,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14408,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +14778,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +14843,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +14969,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15034,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15099,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15164,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15229,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15294,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +15908,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +15973,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16221,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16286,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16351,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +16599,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +16664,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +16851,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +16916,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17347,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17412,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +17599,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +17847,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18095,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18343,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +18896,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +18961,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19026,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20067,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20193,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20258,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20323,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +20571,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +20758,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21006,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21071,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21136,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21323,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21388,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +21514,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +21701,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +21766,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +21831,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22140,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22205,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +22636,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
